--- a/mosip_master/xlsx/doc_type.xlsx
+++ b/mosip_master/xlsx/doc_type.xlsx
@@ -1,23 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Develop_Branch_all\mosip-data\mosip_master\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" tabRatio="500"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$100</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,17 +22,15 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="173">
   <si>
     <t>lang_code</t>
   </si>
@@ -90,6 +83,9 @@
     <t>عقد ايجار</t>
   </si>
   <si>
+    <t>اتفاقية تأجير العنوان</t>
+  </si>
+  <si>
     <t>Contrat de location</t>
   </si>
   <si>
@@ -105,6 +101,12 @@
     <t>Proof of Resident</t>
   </si>
   <si>
+    <t>شهادة الاقامة</t>
+  </si>
+  <si>
+    <t>إثبات مقيم</t>
+  </si>
+  <si>
     <t>Certificat de résidence</t>
   </si>
   <si>
@@ -120,6 +122,12 @@
     <t>Proof of Idendity</t>
   </si>
   <si>
+    <t>جواز سفر</t>
+  </si>
+  <si>
+    <t>إثبات الفكر</t>
+  </si>
+  <si>
     <t>Passeport</t>
   </si>
   <si>
@@ -135,6 +143,12 @@
     <t>Proof relationship of a person</t>
   </si>
   <si>
+    <t>شهادة القرابة</t>
+  </si>
+  <si>
+    <t>إثبات علاقة الشخص</t>
+  </si>
+  <si>
     <t>Certificat de relation</t>
   </si>
   <si>
@@ -150,6 +164,12 @@
     <t>Proof birth and age of a person</t>
   </si>
   <si>
+    <t>شهادة الميلاد</t>
+  </si>
+  <si>
+    <t>إثبات ولادة الشخص وعمره</t>
+  </si>
+  <si>
     <t>Certificat de naissance</t>
   </si>
   <si>
@@ -165,6 +185,9 @@
     <t>Certificate of Exception</t>
   </si>
   <si>
+    <t>شهادة الاستثناء</t>
+  </si>
+  <si>
     <t>Certification dexception</t>
   </si>
   <si>
@@ -393,24 +416,15 @@
     <t>Photo d exception</t>
   </si>
   <si>
-    <t>شهادة الاقامة</t>
-  </si>
-  <si>
-    <t>جواز سفر</t>
-  </si>
-  <si>
-    <t>شهادة القرابة</t>
-  </si>
-  <si>
-    <t>شهادة الميلاد</t>
-  </si>
-  <si>
     <t>بطاقة الطعام</t>
   </si>
   <si>
     <t xml:space="preserve">إما بطاقة تموينية أو بطاقة صور </t>
   </si>
   <si>
+    <t>إما بطاقة تموينية أو بطاقة صور PDS</t>
+  </si>
+  <si>
     <t>بطاقة هوية الناخب</t>
   </si>
   <si>
@@ -468,46 +482,90 @@
     <t>وثيقة استحقاق الأسرة</t>
   </si>
   <si>
-    <t>اتفاقية تأجير العنوان</t>
-  </si>
-  <si>
-    <t>إثبات مقيم</t>
-  </si>
-  <si>
-    <t>إثبات الفكر</t>
-  </si>
-  <si>
-    <t>إثبات علاقة الشخص</t>
-  </si>
-  <si>
-    <t>إثبات ولادة الشخص وعمره</t>
-  </si>
-  <si>
-    <t>إما بطاقة تموينية أو بطاقة صور PDS</t>
-  </si>
-  <si>
     <t>أي مستند استحقاق عائلي صادر عن أي حكومة مركزية أو حكومة ولاية</t>
   </si>
   <si>
     <t>مسجل الميلاد / مؤسسة البلدية أو أي شهادة ميلاد حكومية محلية</t>
   </si>
   <si>
-    <t>شهادة الاستثناء</t>
-  </si>
-  <si>
     <t>إكسبيديشن فوتو</t>
+  </si>
+  <si>
+    <t>LVC</t>
+  </si>
+  <si>
+    <t>Letter from village chief</t>
+  </si>
+  <si>
+    <t>Village verification</t>
+  </si>
+  <si>
+    <t>UTC</t>
+  </si>
+  <si>
+    <t>utility company</t>
+  </si>
+  <si>
+    <t>company verification</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>National Identity Card</t>
+  </si>
+  <si>
+    <t>ID card</t>
+  </si>
+  <si>
+    <t>RSC</t>
+  </si>
+  <si>
+    <t>Resident Card</t>
+  </si>
+  <si>
+    <t>IDT</t>
+  </si>
+  <si>
+    <t>Identity</t>
+  </si>
+  <si>
+    <t>MRC</t>
+  </si>
+  <si>
+    <t>Marriage Certificate</t>
+  </si>
+  <si>
+    <t>proof of marriage</t>
+  </si>
+  <si>
+    <t>AFD</t>
+  </si>
+  <si>
+    <t>Affidavit</t>
+  </si>
+  <si>
+    <t>CBC</t>
+  </si>
+  <si>
+    <t>Copy of Birth Certificate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -520,18 +578,355 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -554,11 +949,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -568,18 +1205,65 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -628,7 +1312,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -663,7 +1347,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -837,29 +1521,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E91"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E100"/>
+  <sheetFormatPr defaultColWidth="8.42857142857143" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="26" style="1" customWidth="1"/>
-    <col min="3" max="3" width="53.42578125" customWidth="1"/>
-    <col min="4" max="4" width="58.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="53.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="58.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="27.8571428571429" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -876,7 +1554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -893,7 +1571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" hidden="1" spans="1:5">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -910,7 +1588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" hidden="1" spans="1:5">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -927,7 +1605,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -944,7 +1622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" hidden="1" spans="1:5">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -955,13 +1633,13 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" hidden="1" spans="1:5">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -969,1432 +1647,1432 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" hidden="1" spans="1:5">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" hidden="1" spans="1:5">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" hidden="1" spans="1:5">
       <c r="A12" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" hidden="1" spans="1:5">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" hidden="1" spans="1:5">
       <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" hidden="1" spans="1:5">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" hidden="1" spans="1:5">
       <c r="A18" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>45</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" hidden="1" spans="1:5">
       <c r="A19" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" hidden="1" spans="1:5">
       <c r="A21" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" hidden="1" spans="1:5">
       <c r="A22" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>5</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>5</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>5</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>5</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>5</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>5</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>5</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D44" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" hidden="1" spans="1:5">
       <c r="A45" t="s">
         <v>11</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" hidden="1" spans="1:5">
       <c r="A46" t="s">
         <v>11</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" hidden="1" spans="1:5">
       <c r="A47" t="s">
         <v>11</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" hidden="1" spans="1:5">
       <c r="A48" t="s">
         <v>11</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" hidden="1" spans="1:5">
       <c r="A49" t="s">
         <v>11</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" hidden="1" spans="1:5">
       <c r="A50" t="s">
         <v>11</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" hidden="1" spans="1:5">
       <c r="A51" t="s">
         <v>11</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D51" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" hidden="1" spans="1:5">
       <c r="A52" t="s">
         <v>11</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C52" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" hidden="1" spans="1:5">
       <c r="A53" t="s">
         <v>11</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" hidden="1" spans="1:5">
       <c r="A54" t="s">
         <v>11</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D54" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" hidden="1" spans="1:5">
       <c r="A55" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" hidden="1" spans="1:5">
       <c r="A56" t="s">
         <v>11</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" hidden="1" spans="1:5">
       <c r="A57" t="s">
         <v>11</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D57" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" hidden="1" spans="1:5">
       <c r="A58" t="s">
         <v>11</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" hidden="1" spans="1:5">
       <c r="A59" t="s">
         <v>11</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D59" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" hidden="1" spans="1:5">
       <c r="A60" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" hidden="1" spans="1:5">
       <c r="A61" t="s">
         <v>11</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" hidden="1" spans="1:5">
       <c r="A62" t="s">
         <v>11</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C62" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" hidden="1" spans="1:5">
       <c r="A63" t="s">
         <v>11</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" hidden="1" spans="1:5">
       <c r="A64" t="s">
         <v>11</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" hidden="1" spans="1:5">
       <c r="A65" t="s">
         <v>11</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" hidden="1" spans="1:5">
       <c r="A66" t="s">
         <v>11</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D66" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>5</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C67" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D67" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" hidden="1" spans="1:5">
       <c r="A68" t="s">
         <v>11</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C68" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D68" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" hidden="1" spans="1:5">
       <c r="A69" t="s">
         <v>9</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D69" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" hidden="1" spans="1:5">
       <c r="A70" t="s">
         <v>9</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" hidden="1" spans="1:5">
       <c r="A71" t="s">
         <v>9</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C71" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D71" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" hidden="1" spans="1:5">
       <c r="A72" t="s">
         <v>9</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D72" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" hidden="1" spans="1:5">
       <c r="A73" t="s">
         <v>9</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D73" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" hidden="1" spans="1:5">
       <c r="A74" t="s">
         <v>9</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D74" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" hidden="1" spans="1:5">
       <c r="A75" t="s">
         <v>9</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D75" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" hidden="1" spans="1:5">
       <c r="A76" t="s">
         <v>9</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D76" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" hidden="1" spans="1:5">
       <c r="A77" t="s">
         <v>9</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C77" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D77" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" hidden="1" spans="1:5">
       <c r="A78" t="s">
         <v>9</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D78" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" hidden="1" spans="1:5">
       <c r="A79" t="s">
         <v>9</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C79" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D79" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" hidden="1" spans="1:5">
       <c r="A80" t="s">
         <v>9</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C80" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D80" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" hidden="1" spans="1:5">
       <c r="A81" t="s">
         <v>9</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C81" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D81" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" hidden="1" spans="1:5">
       <c r="A82" t="s">
         <v>9</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C82" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D82" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" hidden="1" spans="1:5">
       <c r="A83" t="s">
         <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" hidden="1" spans="1:5">
       <c r="A84" t="s">
         <v>9</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D84" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" hidden="1" spans="1:5">
       <c r="A85" t="s">
         <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D85" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" hidden="1" spans="1:5">
       <c r="A86" t="s">
         <v>9</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D86" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" hidden="1" spans="1:5">
       <c r="A87" t="s">
         <v>9</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D87" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" hidden="1" spans="1:5">
       <c r="A88" t="s">
         <v>9</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D88" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" hidden="1" spans="1:5">
       <c r="A89" t="s">
         <v>9</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D89" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" hidden="1" spans="1:5">
       <c r="A90" t="s">
         <v>9</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C90" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" hidden="1" spans="1:5">
       <c r="A91" t="s">
         <v>9</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C91" t="s">
         <v>152</v>
@@ -2406,15 +3084,170 @@
         <v>8</v>
       </c>
     </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>5</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E91">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E100" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <filters>
-        <filter val="fra"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="eng"/>
+      </customFilters>
     </filterColumn>
+    <extLst/>
   </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/mosip_master/xlsx/doc_type.xlsx
+++ b/mosip_master/xlsx/doc_type.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="173">
   <si>
     <t>lang_code</t>
   </si>
@@ -158,337 +158,337 @@
     <t>COB</t>
   </si>
   <si>
+    <t>شهادة الميلاد</t>
+  </si>
+  <si>
+    <t>إثبات ولادة الشخص وعمره</t>
+  </si>
+  <si>
+    <t>Certificat de naissance</t>
+  </si>
+  <si>
+    <t>Preuve de naissance et âge dune personne</t>
+  </si>
+  <si>
+    <t>COE</t>
+  </si>
+  <si>
+    <t>Certification of Exception</t>
+  </si>
+  <si>
+    <t>Certificate of Exception</t>
+  </si>
+  <si>
+    <t>شهادة الاستثناء</t>
+  </si>
+  <si>
+    <t>Certification dexception</t>
+  </si>
+  <si>
+    <t>DOC002</t>
+  </si>
+  <si>
+    <t>PAN card</t>
+  </si>
+  <si>
+    <t>DOC003</t>
+  </si>
+  <si>
+    <t>Either Ration or PDS Photo card</t>
+  </si>
+  <si>
+    <t>DOC004</t>
+  </si>
+  <si>
+    <t>Voter Identification card</t>
+  </si>
+  <si>
+    <t>DOC005</t>
+  </si>
+  <si>
+    <t>Driving licence of the applicant</t>
+  </si>
+  <si>
+    <t>DOC006</t>
+  </si>
+  <si>
+    <t>Photo identification cards issued by the Government</t>
+  </si>
+  <si>
+    <t>DOC007</t>
+  </si>
+  <si>
+    <t>Service photo ID cards that is issued by a PSU</t>
+  </si>
+  <si>
+    <t>DOC008</t>
+  </si>
+  <si>
+    <t>Licence of Arms</t>
+  </si>
+  <si>
+    <t>DOC009</t>
+  </si>
+  <si>
+    <t>Photo Bank ATM card</t>
+  </si>
+  <si>
+    <t>DOC010</t>
+  </si>
+  <si>
+    <t>Photo Credit card</t>
+  </si>
+  <si>
+    <t>DOC011</t>
+  </si>
+  <si>
+    <t>Photo card of the Freedom Fighter</t>
+  </si>
+  <si>
+    <t>DOC012</t>
+  </si>
+  <si>
+    <t>Certificate of Marriage</t>
+  </si>
+  <si>
+    <t>DOC013</t>
+  </si>
+  <si>
+    <t>Passbook or Bank Statement</t>
+  </si>
+  <si>
+    <t>DOC014</t>
+  </si>
+  <si>
+    <t>Account statement or passbook of the Post Office</t>
+  </si>
+  <si>
+    <t>DOC015</t>
+  </si>
+  <si>
+    <t>Ration Card</t>
+  </si>
+  <si>
+    <t>DOC016</t>
+  </si>
+  <si>
+    <t>PSU issued Service photo ID card with address</t>
+  </si>
+  <si>
+    <t>DOC017</t>
+  </si>
+  <si>
+    <t>Previous 3 months’ electricity bill</t>
+  </si>
+  <si>
+    <t>DOC018</t>
+  </si>
+  <si>
+    <t>Water bill as long as it is not more than 3 months’ old</t>
+  </si>
+  <si>
+    <t>DOC024</t>
+  </si>
+  <si>
+    <t>PDS Card</t>
+  </si>
+  <si>
+    <t>DOC025</t>
+  </si>
+  <si>
+    <t>Medical card issued by the State Govt, CGHS, ECHS and ESIC</t>
+  </si>
+  <si>
+    <t>Medical card issued by the State Government, CGHS, ECHS and also ESIC</t>
+  </si>
+  <si>
+    <t>DOC026</t>
+  </si>
+  <si>
+    <t>Canteen card of the Army</t>
+  </si>
+  <si>
+    <t>DOC027</t>
+  </si>
+  <si>
+    <t>Family entitlement document</t>
+  </si>
+  <si>
+    <t>Any family entitlement document issued by any Central or State Government</t>
+  </si>
+  <si>
+    <t>DOC028</t>
+  </si>
+  <si>
+    <t>Birth Certificate</t>
+  </si>
+  <si>
+    <t>Registrar of Birth/municipal Corporation or any local government Birth Certificate</t>
+  </si>
+  <si>
+    <t>Carte PAN</t>
+  </si>
+  <si>
+    <t>Soit ration ou PDS photo carte</t>
+  </si>
+  <si>
+    <t>Carte d’identification des électeurs</t>
+  </si>
+  <si>
+    <t>Permis de conduire du demandeur</t>
+  </si>
+  <si>
+    <t>Cartes d’identité photo émises par le gouvernement</t>
+  </si>
+  <si>
+    <t>Cartes d’identité de service de photo émises par un PSU</t>
+  </si>
+  <si>
+    <t>Licence d’armes</t>
+  </si>
+  <si>
+    <t>Photo banque carte bancaire</t>
+  </si>
+  <si>
+    <t>Carte de crédit photo</t>
+  </si>
+  <si>
+    <t>Carte photo du Freedom Fighter</t>
+  </si>
+  <si>
+    <t>Certificat de mariage</t>
+  </si>
+  <si>
+    <t>Livret ou relevé bancaire</t>
+  </si>
+  <si>
+    <t>Relevé de compte ou livret du Bureau de poste</t>
+  </si>
+  <si>
+    <t>Carte de ration</t>
+  </si>
+  <si>
+    <t>PSU a émis la carte didentité de photo de service avec ladresse</t>
+  </si>
+  <si>
+    <t>PSU a émis la carte d’identité de photo de service avec l’adresse</t>
+  </si>
+  <si>
+    <t>Facture d’électricité précédente de 3 mois</t>
+  </si>
+  <si>
+    <t>Facture d’eau tant qu’elle n’a pas plus de 3 mois</t>
+  </si>
+  <si>
+    <t>Carte PDS</t>
+  </si>
+  <si>
+    <t>Carte médicale délivrée par le govt de l'État</t>
+  </si>
+  <si>
+    <t>Carte médicale délivrée par le gouvernement de l’État, le CGHS, l’ECHS et également l’ESIC</t>
+  </si>
+  <si>
+    <t>Carte de cantine de l’armée</t>
+  </si>
+  <si>
+    <t>Titre de droit familial</t>
+  </si>
+  <si>
+    <t>Tout document de droit de la famille délivré par un gouvernement central ou</t>
+  </si>
+  <si>
+    <t>Registraire de naissance/municipalité ou tout acte de naissance du gouvernement local</t>
+  </si>
+  <si>
+    <t>EOP</t>
+  </si>
+  <si>
+    <t>Expetion Photo</t>
+  </si>
+  <si>
+    <t>Photo d exception</t>
+  </si>
+  <si>
+    <t>بطاقة الطعام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إما بطاقة تموينية أو بطاقة صور </t>
+  </si>
+  <si>
+    <t>إما بطاقة تموينية أو بطاقة صور PDS</t>
+  </si>
+  <si>
+    <t>بطاقة هوية الناخب</t>
+  </si>
+  <si>
+    <t>رخصة القيادة لمقدم الطلب</t>
+  </si>
+  <si>
+    <t>بطاقات هوية مصورة صادرة عن الحكومة</t>
+  </si>
+  <si>
+    <t>بطاقات هوية تحمل صورة الخدمة الصادرة عن PSU</t>
+  </si>
+  <si>
+    <t>رخصة السلاح</t>
+  </si>
+  <si>
+    <t>بطاقة الصراف الآلي لبنك الصور</t>
+  </si>
+  <si>
+    <t>بطاقة ائتمان الصور</t>
+  </si>
+  <si>
+    <t>بطاقة مصورة لمقاتل الحرية</t>
+  </si>
+  <si>
+    <t>عقد زواج</t>
+  </si>
+  <si>
+    <t>دفتر حسابات أو كشف حساب بنكي</t>
+  </si>
+  <si>
+    <t>كشف حساب أو دفتر مرور لمكتب البريد</t>
+  </si>
+  <si>
+    <t>البطاقة التموينية</t>
+  </si>
+  <si>
+    <t>أصدرت PSU بطاقة هوية تحمل صورة الخدمة مع العنوان</t>
+  </si>
+  <si>
+    <t>فاتورة الكهرباء عن الثلاثة أشهر السابقة</t>
+  </si>
+  <si>
+    <t>فاتورة المياه بشرط ألا تزيد عن 3 أشهر</t>
+  </si>
+  <si>
+    <t>بطاقة PDS</t>
+  </si>
+  <si>
+    <t>بطاقة طبية صادرة عن حكومة الدولة و CGHS و ECHS و ESIC</t>
+  </si>
+  <si>
+    <t>بطاقة مقصف للجيش</t>
+  </si>
+  <si>
+    <t>وثيقة استحقاق الأسرة</t>
+  </si>
+  <si>
+    <t>أي مستند استحقاق عائلي صادر عن أي حكومة مركزية أو حكومة ولاية</t>
+  </si>
+  <si>
+    <t>مسجل الميلاد / مؤسسة البلدية أو أي شهادة ميلاد حكومية محلية</t>
+  </si>
+  <si>
+    <t>إكسبيديشن فوتو</t>
+  </si>
+  <si>
     <t>Certificate of Birth</t>
   </si>
   <si>
     <t>Proof birth and age of a person</t>
-  </si>
-  <si>
-    <t>شهادة الميلاد</t>
-  </si>
-  <si>
-    <t>إثبات ولادة الشخص وعمره</t>
-  </si>
-  <si>
-    <t>Certificat de naissance</t>
-  </si>
-  <si>
-    <t>Preuve de naissance et âge dune personne</t>
-  </si>
-  <si>
-    <t>COE</t>
-  </si>
-  <si>
-    <t>Certification of Exception</t>
-  </si>
-  <si>
-    <t>Certificate of Exception</t>
-  </si>
-  <si>
-    <t>شهادة الاستثناء</t>
-  </si>
-  <si>
-    <t>Certification dexception</t>
-  </si>
-  <si>
-    <t>DOC002</t>
-  </si>
-  <si>
-    <t>PAN card</t>
-  </si>
-  <si>
-    <t>DOC003</t>
-  </si>
-  <si>
-    <t>Either Ration or PDS Photo card</t>
-  </si>
-  <si>
-    <t>DOC004</t>
-  </si>
-  <si>
-    <t>Voter Identification card</t>
-  </si>
-  <si>
-    <t>DOC005</t>
-  </si>
-  <si>
-    <t>Driving licence of the applicant</t>
-  </si>
-  <si>
-    <t>DOC006</t>
-  </si>
-  <si>
-    <t>Photo identification cards issued by the Government</t>
-  </si>
-  <si>
-    <t>DOC007</t>
-  </si>
-  <si>
-    <t>Service photo ID cards that is issued by a PSU</t>
-  </si>
-  <si>
-    <t>DOC008</t>
-  </si>
-  <si>
-    <t>Licence of Arms</t>
-  </si>
-  <si>
-    <t>DOC009</t>
-  </si>
-  <si>
-    <t>Photo Bank ATM card</t>
-  </si>
-  <si>
-    <t>DOC010</t>
-  </si>
-  <si>
-    <t>Photo Credit card</t>
-  </si>
-  <si>
-    <t>DOC011</t>
-  </si>
-  <si>
-    <t>Photo card of the Freedom Fighter</t>
-  </si>
-  <si>
-    <t>DOC012</t>
-  </si>
-  <si>
-    <t>Certificate of Marriage</t>
-  </si>
-  <si>
-    <t>DOC013</t>
-  </si>
-  <si>
-    <t>Passbook or Bank Statement</t>
-  </si>
-  <si>
-    <t>DOC014</t>
-  </si>
-  <si>
-    <t>Account statement or passbook of the Post Office</t>
-  </si>
-  <si>
-    <t>DOC015</t>
-  </si>
-  <si>
-    <t>Ration Card</t>
-  </si>
-  <si>
-    <t>DOC016</t>
-  </si>
-  <si>
-    <t>PSU issued Service photo ID card with address</t>
-  </si>
-  <si>
-    <t>DOC017</t>
-  </si>
-  <si>
-    <t>Previous 3 months’ electricity bill</t>
-  </si>
-  <si>
-    <t>DOC018</t>
-  </si>
-  <si>
-    <t>Water bill as long as it is not more than 3 months’ old</t>
-  </si>
-  <si>
-    <t>DOC024</t>
-  </si>
-  <si>
-    <t>PDS Card</t>
-  </si>
-  <si>
-    <t>DOC025</t>
-  </si>
-  <si>
-    <t>Medical card issued by the State Govt, CGHS, ECHS and ESIC</t>
-  </si>
-  <si>
-    <t>Medical card issued by the State Government, CGHS, ECHS and also ESIC</t>
-  </si>
-  <si>
-    <t>DOC026</t>
-  </si>
-  <si>
-    <t>Canteen card of the Army</t>
-  </si>
-  <si>
-    <t>DOC027</t>
-  </si>
-  <si>
-    <t>Family entitlement document</t>
-  </si>
-  <si>
-    <t>Any family entitlement document issued by any Central or State Government</t>
-  </si>
-  <si>
-    <t>DOC028</t>
-  </si>
-  <si>
-    <t>Birth Certificate</t>
-  </si>
-  <si>
-    <t>Registrar of Birth/municipal Corporation or any local government Birth Certificate</t>
-  </si>
-  <si>
-    <t>Carte PAN</t>
-  </si>
-  <si>
-    <t>Soit ration ou PDS photo carte</t>
-  </si>
-  <si>
-    <t>Carte d’identification des électeurs</t>
-  </si>
-  <si>
-    <t>Permis de conduire du demandeur</t>
-  </si>
-  <si>
-    <t>Cartes d’identité photo émises par le gouvernement</t>
-  </si>
-  <si>
-    <t>Cartes d’identité de service de photo émises par un PSU</t>
-  </si>
-  <si>
-    <t>Licence d’armes</t>
-  </si>
-  <si>
-    <t>Photo banque carte bancaire</t>
-  </si>
-  <si>
-    <t>Carte de crédit photo</t>
-  </si>
-  <si>
-    <t>Carte photo du Freedom Fighter</t>
-  </si>
-  <si>
-    <t>Certificat de mariage</t>
-  </si>
-  <si>
-    <t>Livret ou relevé bancaire</t>
-  </si>
-  <si>
-    <t>Relevé de compte ou livret du Bureau de poste</t>
-  </si>
-  <si>
-    <t>Carte de ration</t>
-  </si>
-  <si>
-    <t>PSU a émis la carte didentité de photo de service avec ladresse</t>
-  </si>
-  <si>
-    <t>PSU a émis la carte d’identité de photo de service avec l’adresse</t>
-  </si>
-  <si>
-    <t>Facture d’électricité précédente de 3 mois</t>
-  </si>
-  <si>
-    <t>Facture d’eau tant qu’elle n’a pas plus de 3 mois</t>
-  </si>
-  <si>
-    <t>Carte PDS</t>
-  </si>
-  <si>
-    <t>Carte médicale délivrée par le govt de l'État</t>
-  </si>
-  <si>
-    <t>Carte médicale délivrée par le gouvernement de l’État, le CGHS, l’ECHS et également l’ESIC</t>
-  </si>
-  <si>
-    <t>Carte de cantine de l’armée</t>
-  </si>
-  <si>
-    <t>Titre de droit familial</t>
-  </si>
-  <si>
-    <t>Tout document de droit de la famille délivré par un gouvernement central ou</t>
-  </si>
-  <si>
-    <t>Registraire de naissance/municipalité ou tout acte de naissance du gouvernement local</t>
-  </si>
-  <si>
-    <t>EOP</t>
-  </si>
-  <si>
-    <t>Expetion Photo</t>
-  </si>
-  <si>
-    <t>Photo d exception</t>
-  </si>
-  <si>
-    <t>بطاقة الطعام</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إما بطاقة تموينية أو بطاقة صور </t>
-  </si>
-  <si>
-    <t>إما بطاقة تموينية أو بطاقة صور PDS</t>
-  </si>
-  <si>
-    <t>بطاقة هوية الناخب</t>
-  </si>
-  <si>
-    <t>رخصة القيادة لمقدم الطلب</t>
-  </si>
-  <si>
-    <t>بطاقات هوية مصورة صادرة عن الحكومة</t>
-  </si>
-  <si>
-    <t>بطاقات هوية تحمل صورة الخدمة الصادرة عن PSU</t>
-  </si>
-  <si>
-    <t>رخصة السلاح</t>
-  </si>
-  <si>
-    <t>بطاقة الصراف الآلي لبنك الصور</t>
-  </si>
-  <si>
-    <t>بطاقة ائتمان الصور</t>
-  </si>
-  <si>
-    <t>بطاقة مصورة لمقاتل الحرية</t>
-  </si>
-  <si>
-    <t>عقد زواج</t>
-  </si>
-  <si>
-    <t>دفتر حسابات أو كشف حساب بنكي</t>
-  </si>
-  <si>
-    <t>كشف حساب أو دفتر مرور لمكتب البريد</t>
-  </si>
-  <si>
-    <t>البطاقة التموينية</t>
-  </si>
-  <si>
-    <t>أصدرت PSU بطاقة هوية تحمل صورة الخدمة مع العنوان</t>
-  </si>
-  <si>
-    <t>فاتورة الكهرباء عن الثلاثة أشهر السابقة</t>
-  </si>
-  <si>
-    <t>فاتورة المياه بشرط ألا تزيد عن 3 أشهر</t>
-  </si>
-  <si>
-    <t>بطاقة PDS</t>
-  </si>
-  <si>
-    <t>بطاقة طبية صادرة عن حكومة الدولة و CGHS و ECHS و ESIC</t>
-  </si>
-  <si>
-    <t>بطاقة مقصف للجيش</t>
-  </si>
-  <si>
-    <t>وثيقة استحقاق الأسرة</t>
-  </si>
-  <si>
-    <t>أي مستند استحقاق عائلي صادر عن أي حكومة مركزية أو حكومة ولاية</t>
-  </si>
-  <si>
-    <t>مسجل الميلاد / مؤسسة البلدية أو أي شهادة ميلاد حكومية محلية</t>
-  </si>
-  <si>
-    <t>إكسبيديشن فوتو</t>
   </si>
   <si>
     <t>LVC</t>
@@ -1527,7 +1527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr defaultColWidth="8.42857142857143" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="25.1428571428571" customWidth="1"/>
@@ -1809,9 +1809,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" hidden="1" spans="1:5">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>41</v>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="18" hidden="1" spans="1:5">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>41</v>
@@ -1843,35 +1843,35 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" hidden="1" spans="1:5">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C20" t="s">
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>
@@ -1879,27 +1879,27 @@
     </row>
     <row r="21" hidden="1" spans="1:5">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" hidden="1" spans="1:5">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C22" t="s">
         <v>52</v>
@@ -2211,7 +2211,7 @@
         <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>8</v>
@@ -2222,10 +2222,10 @@
         <v>5</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
         <v>91</v>
@@ -2245,7 +2245,7 @@
         <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>8</v>
@@ -2256,30 +2256,30 @@
         <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" hidden="1" spans="1:5">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
         <v>98</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>8</v>
@@ -2293,10 +2293,10 @@
         <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>8</v>
@@ -2310,10 +2310,10 @@
         <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>8</v>
@@ -2327,10 +2327,10 @@
         <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>8</v>
@@ -2344,10 +2344,10 @@
         <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>8</v>
@@ -2361,10 +2361,10 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>8</v>
@@ -2378,10 +2378,10 @@
         <v>63</v>
       </c>
       <c r="C50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>8</v>
@@ -2395,10 +2395,10 @@
         <v>65</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>8</v>
@@ -2412,10 +2412,10 @@
         <v>67</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>8</v>
@@ -2429,10 +2429,10 @@
         <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>8</v>
@@ -2446,10 +2446,10 @@
         <v>71</v>
       </c>
       <c r="C54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>8</v>
@@ -2463,10 +2463,10 @@
         <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>8</v>
@@ -2480,10 +2480,10 @@
         <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D56" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>8</v>
@@ -2497,10 +2497,10 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>8</v>
@@ -2514,7 +2514,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
         <v>113</v>
@@ -2534,7 +2534,7 @@
         <v>114</v>
       </c>
       <c r="D59" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>8</v>
@@ -2548,10 +2548,10 @@
         <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D60" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
@@ -2565,10 +2565,10 @@
         <v>85</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
@@ -2582,7 +2582,7 @@
         <v>87</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D62" t="s">
         <v>118</v>
@@ -2596,13 +2596,13 @@
         <v>11</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C63" t="s">
         <v>119</v>
       </c>
       <c r="D63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>8</v>
@@ -2616,7 +2616,7 @@
         <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D64" t="s">
         <v>121</v>
@@ -2630,27 +2630,27 @@
         <v>11</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" t="s">
         <v>122</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" hidden="1" spans="1:5">
-      <c r="A66" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="C66" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
         <v>124</v>
@@ -2659,18 +2659,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" hidden="1" spans="1:5">
       <c r="A67" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" t="s">
         <v>125</v>
       </c>
-      <c r="C67" t="s">
-        <v>126</v>
-      </c>
       <c r="D67" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>8</v>
@@ -2678,13 +2678,13 @@
     </row>
     <row r="68" hidden="1" spans="1:5">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="C68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D68" t="s">
         <v>126</v>
@@ -2701,7 +2701,7 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D69" t="s">
         <v>128</v>
@@ -2721,7 +2721,7 @@
         <v>129</v>
       </c>
       <c r="D70" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -2735,10 +2735,10 @@
         <v>57</v>
       </c>
       <c r="C71" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D71" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
@@ -2752,10 +2752,10 @@
         <v>59</v>
       </c>
       <c r="C72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>8</v>
@@ -2769,10 +2769,10 @@
         <v>61</v>
       </c>
       <c r="C73" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D73" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
@@ -2786,10 +2786,10 @@
         <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>8</v>
@@ -2803,10 +2803,10 @@
         <v>65</v>
       </c>
       <c r="C75" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D75" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>8</v>
@@ -2820,10 +2820,10 @@
         <v>67</v>
       </c>
       <c r="C76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>8</v>
@@ -2837,10 +2837,10 @@
         <v>69</v>
       </c>
       <c r="C77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>8</v>
@@ -2854,10 +2854,10 @@
         <v>71</v>
       </c>
       <c r="C78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
@@ -2871,10 +2871,10 @@
         <v>73</v>
       </c>
       <c r="C79" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D79" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
@@ -2888,10 +2888,10 @@
         <v>75</v>
       </c>
       <c r="C80" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D80" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>8</v>
@@ -2905,10 +2905,10 @@
         <v>77</v>
       </c>
       <c r="C81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>8</v>
@@ -2922,10 +2922,10 @@
         <v>79</v>
       </c>
       <c r="C82" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D82" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>8</v>
@@ -2939,10 +2939,10 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>8</v>
@@ -2956,10 +2956,10 @@
         <v>83</v>
       </c>
       <c r="C84" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D84" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>8</v>
@@ -2969,14 +2969,14 @@
       <c r="A85" t="s">
         <v>9</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D85" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>8</v>
@@ -2986,14 +2986,14 @@
       <c r="A86" t="s">
         <v>9</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
@@ -3004,13 +3004,13 @@
         <v>9</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C87" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D87" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
@@ -3024,7 +3024,7 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D88" t="s">
         <v>148</v>
@@ -3038,13 +3038,13 @@
         <v>9</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C89" t="s">
+        <v>42</v>
+      </c>
+      <c r="D89" t="s">
         <v>149</v>
-      </c>
-      <c r="D89" t="s">
-        <v>150</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
@@ -3055,29 +3055,29 @@
         <v>9</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="D90" t="s">
+        <v>150</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" hidden="1" spans="1:5">
-      <c r="A91" t="s">
-        <v>9</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C91" t="s">
-        <v>152</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="D91" s="5" t="s">
         <v>152</v>
       </c>
       <c r="E91" s="1" t="s">
@@ -3089,13 +3089,13 @@
         <v>5</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>8</v>
@@ -3106,13 +3106,13 @@
         <v>5</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>8</v>
@@ -3123,13 +3123,13 @@
         <v>5</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>8</v>
@@ -3140,13 +3140,13 @@
         <v>5</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>161</v>
+        <v>22</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>8</v>
@@ -3157,13 +3157,13 @@
         <v>5</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>8</v>
@@ -3174,13 +3174,13 @@
         <v>5</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>29</v>
+        <v>168</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
@@ -3191,10 +3191,10 @@
         <v>5</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>168</v>
@@ -3208,37 +3208,20 @@
         <v>5</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
-      <c r="A100" t="s">
-        <v>5</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E100" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E99" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="equal" val="eng"/>
